--- a/data/trans_orig/P21D_6_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14248</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224666</t>
+          <t>225014</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324647</t>
+          <t>323742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>332603</t>
+          <t>332095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>552476</t>
+          <t>553127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561754</t>
+          <t>562238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>26837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1101562</t>
+          <t>1101645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1114296</t>
+          <t>1114588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>917298</t>
+          <t>917131</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>930371</t>
+          <t>930751</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2025367</t>
+          <t>2026579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2042905</t>
+          <t>2043510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304490</t>
+          <t>304036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>309566</t>
+          <t>309694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615810</t>
+          <t>615360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>621949</t>
+          <t>621953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28248</t>
+          <t>28812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42106</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1639054</t>
+          <t>1639515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1653047</t>
+          <t>1653009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1557979</t>
+          <t>1557415</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1572693</t>
+          <t>1572796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3200505</t>
+          <t>3202029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3222494</t>
+          <t>3223240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_6_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>229093</t>
+          <t>251657</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225014</t>
+          <t>247573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230097</t>
+          <t>252652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>329150</t>
+          <t>354705</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323742</t>
+          <t>349287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>332095</t>
+          <t>357842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>558243</t>
+          <t>606362</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>553127</t>
+          <t>600465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562238</t>
+          <t>610472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>230097</t>
+          <t>252652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>230097</t>
+          <t>252652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230097</t>
+          <t>252652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>336627</t>
+          <t>362528</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>336627</t>
+          <t>362528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>336627</t>
+          <t>362528</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>566724</t>
+          <t>615180</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>566724</t>
+          <t>615180</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>566724</t>
+          <t>615180</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>18502</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1110194</t>
+          <t>952601</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1101645</t>
+          <t>944404</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1114588</t>
+          <t>956623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>925384</t>
+          <t>972923</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>917131</t>
+          <t>965596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>930751</t>
+          <t>978124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2035578</t>
+          <t>1925523</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2026579</t>
+          <t>1915185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2043510</t>
+          <t>1932000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1116103</t>
+          <t>958507</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1116103</t>
+          <t>958507</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1116103</t>
+          <t>958507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2053416</t>
+          <t>1944025</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2053416</t>
+          <t>1944025</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2053416</t>
+          <t>1944025</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>308499</t>
+          <t>345478</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304036</t>
+          <t>339593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>311772</t>
+          <t>341730</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>309694</t>
+          <t>339568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>620272</t>
+          <t>687208</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615360</t>
+          <t>682632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>621953</t>
+          <t>688942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,93%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28812</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1647787</t>
+          <t>1549737</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1639515</t>
+          <t>1541215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1653009</t>
+          <t>1554488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1566306</t>
+          <t>1669357</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1557415</t>
+          <t>1661732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1572796</t>
+          <t>1676116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,22 +1937,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3214093</t>
+          <t>3219094</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3202029</t>
+          <t>3208152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3223240</t>
+          <t>3227878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1656384</t>
+          <t>1558368</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1656384</t>
+          <t>1558368</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1656384</t>
+          <t>1558368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1586227</t>
+          <t>1690286</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1586227</t>
+          <t>1690286</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1586227</t>
+          <t>1690286</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3242611</t>
+          <t>3248654</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3242611</t>
+          <t>3248654</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3242611</t>
+          <t>3248654</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
